--- a/Teste_Requisições _ Topografia.xlsx
+++ b/Teste_Requisições _ Topografia.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Desktop\Dev\TopTest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Desktop\TopogfRegisto-DEV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3894EBFE-6382-4534-BA75-05F303E89F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14AE35A-C843-44B1-AAAC-B46A5421EA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" xr2:uid="{27465798-F3B3-4AB2-AA5D-2EABD83C4153}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="62">
   <si>
     <t>DATA</t>
   </si>
@@ -123,60 +123,12 @@
     <t>Continua</t>
   </si>
   <si>
-    <t>Francisco</t>
-  </si>
-  <si>
-    <t>Eng teste</t>
-  </si>
-  <si>
-    <t>Empresa Teste</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>OBRA FAMALICAO</t>
-  </si>
-  <si>
-    <t>wer</t>
-  </si>
-  <si>
     <t>OBSERVAÇAO</t>
   </si>
   <si>
-    <t>Outros</t>
-  </si>
-  <si>
-    <t>Famalicao</t>
-  </si>
-  <si>
-    <t>Planta limites do terreno</t>
-  </si>
-  <si>
     <t>Whatsapp</t>
   </si>
   <si>
-    <t>VENDEIRO</t>
-  </si>
-  <si>
-    <t>P VARZIM</t>
-  </si>
-  <si>
-    <t>IMPLANTAR ESTRUTURAS PISO 1</t>
-  </si>
-  <si>
-    <t>EmppresaGrowTeste</t>
-  </si>
-  <si>
-    <t>PRIME</t>
-  </si>
-  <si>
-    <t>LIMITES TERRENO E MOVIMENTO TERRAS</t>
-  </si>
-  <si>
-    <t>Terreno com bastantes relevos e areosa</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Vermelho (Data Ultrapassada)</t>
   </si>
   <si>
@@ -189,12 +141,6 @@
     <t>Cinzento (Faltam 7 dias ou menos)</t>
   </si>
   <si>
-    <t>FranciscoTeste</t>
-  </si>
-  <si>
-    <t>serviçoSolicitado</t>
-  </si>
-  <si>
     <t>TEMPO DEDICADO AO TRABALHO (S/Deslocação)</t>
   </si>
   <si>
@@ -231,30 +177,6 @@
     <t>EXTERNO</t>
   </si>
   <si>
-    <t>Outro</t>
-  </si>
-  <si>
-    <t>Levantamento</t>
-  </si>
-  <si>
-    <t>TesteObra</t>
-  </si>
-  <si>
-    <t>Lisboa</t>
-  </si>
-  <si>
-    <t>asd</t>
-  </si>
-  <si>
-    <t>OutroTesteVia</t>
-  </si>
-  <si>
-    <t>Obrasdasdasd</t>
-  </si>
-  <si>
-    <t>ConcelhoTeste</t>
-  </si>
-  <si>
     <t>TÉCNICO*</t>
   </si>
   <si>
@@ -288,52 +210,22 @@
     <t>PEDIDO*</t>
   </si>
   <si>
-    <t>Arquiteto Manel</t>
-  </si>
-  <si>
-    <t>TesteOutroVia</t>
-  </si>
-  <si>
-    <t>P varzim</t>
-  </si>
-  <si>
-    <t>ConcelhoTesteOutro</t>
-  </si>
-  <si>
-    <t>levantamento</t>
-  </si>
-  <si>
-    <t>sdf</t>
-  </si>
-  <si>
-    <t>asdas</t>
-  </si>
-  <si>
-    <t>LisboaTeste</t>
-  </si>
-  <si>
-    <t>sda</t>
-  </si>
-  <si>
-    <t>Pombo correio</t>
-  </si>
-  <si>
     <t>Vendeiro</t>
   </si>
   <si>
-    <t>Engenheiro Testew</t>
-  </si>
-  <si>
-    <t>ViaOutro Teste</t>
-  </si>
-  <si>
-    <t>Residencias Viana do Castelo</t>
-  </si>
-  <si>
-    <t>Viana do Castelo</t>
-  </si>
-  <si>
-    <t>Levantamento terreno</t>
+    <t>Daniel+Francisco</t>
+  </si>
+  <si>
+    <t>Nuno Macedo</t>
+  </si>
+  <si>
+    <t>Implantação de maciços bloco D</t>
+  </si>
+  <si>
+    <t>Única</t>
+  </si>
+  <si>
+    <t>Pendente</t>
   </si>
 </sst>
 </file>
@@ -344,7 +236,7 @@
     <numFmt numFmtId="164" formatCode="[$-F400]h:mm:ss\ AM/PM"/>
     <numFmt numFmtId="165" formatCode="h:mm;@"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -364,6 +256,12 @@
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -435,10 +333,16 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -447,7 +351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -458,49 +362,58 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -916,20 +829,20 @@
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="16.5546875" style="8" customWidth="1"/>
+    <col min="3" max="3" width="16.5546875" style="5" customWidth="1"/>
     <col min="4" max="4" width="12.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="20.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="19.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="32.21875" style="1" customWidth="1"/>
     <col min="10" max="10" width="30.44140625" style="1" customWidth="1"/>
     <col min="11" max="11" width="46" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="45.33203125" style="8" customWidth="1"/>
-    <col min="14" max="14" width="28.109375" style="8" customWidth="1"/>
-    <col min="15" max="15" width="45.33203125" style="8" customWidth="1"/>
+    <col min="12" max="13" width="45.33203125" style="5" customWidth="1"/>
+    <col min="14" max="14" width="28.109375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="45.33203125" style="5" customWidth="1"/>
     <col min="16" max="16" width="12.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="8.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="9.109375" style="3"/>
     <col min="19" max="19" width="28.44140625" style="3" customWidth="1"/>
     <col min="20" max="20" width="100" style="1" customWidth="1"/>
@@ -937,105 +850,117 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" s="18"/>
+      <c r="J1" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="K1" s="17"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="15"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="S2" s="1"/>
+    </row>
+    <row r="3" spans="1:19" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="19" t="s">
+      <c r="D3" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="21"/>
+      <c r="F3" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="21" t="s">
+      <c r="G3" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="I1" s="21"/>
-      <c r="J1" s="20" t="s">
+      <c r="H3" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="K1" s="20"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="S1" s="1"/>
-    </row>
-    <row r="2" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
-      <c r="S2" s="1"/>
-    </row>
-    <row r="3" spans="1:19" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D3" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" s="17"/>
-      <c r="P3" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q3" s="17"/>
+      <c r="I3" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="O3" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="P3" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q3" s="21"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="D4" s="5" t="s">
+    <row r="4" spans="1:19" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="19"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="P4" s="5" t="s">
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="Q4" s="10" t="s">
+      <c r="Q4" s="23" t="s">
         <v>1</v>
       </c>
       <c r="S4" s="1"/>
@@ -1044,41 +969,49 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="2">
-        <v>46160</v>
-      </c>
-      <c r="E5" s="9">
-        <v>0.70000000000000007</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H5" s="1" t="s">
+      <c r="C5" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D5" s="13">
+        <v>46182</v>
+      </c>
+      <c r="E5" s="14">
+        <v>0.59583333333333333</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="L5" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P5" s="2">
-        <v>46160</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>0.86736111111111114</v>
+      <c r="I5" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="J5" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K5" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="O5" s="12"/>
+      <c r="P5" s="13">
+        <v>46189</v>
+      </c>
+      <c r="Q5" s="14">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="R5" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="S5" s="1"/>
     </row>
@@ -1086,654 +1019,88 @@
       <c r="B6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D6" s="2">
-        <v>46160</v>
-      </c>
-      <c r="E6" s="9">
-        <v>0.72638888888888886</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P6" s="2">
-        <v>46162</v>
-      </c>
-      <c r="Q6" s="9">
-        <v>0.73541666666666661</v>
-      </c>
       <c r="S6" s="1"/>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="2">
-        <v>46160</v>
-      </c>
-      <c r="E7" s="9">
-        <v>0.73541666666666661</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P7" s="2">
-        <v>46168</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>0.73611111111111116</v>
-      </c>
       <c r="S7" s="1"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B8" s="1">
         <v>4</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="2">
-        <v>46160</v>
-      </c>
-      <c r="E8" s="9">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="L8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="P8" s="2">
-        <v>46161</v>
-      </c>
-      <c r="Q8" s="9">
-        <v>0.73611111111111116</v>
-      </c>
       <c r="S8" s="1"/>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B9" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D9" s="2">
-        <v>46160</v>
-      </c>
-      <c r="E9" s="9">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" s="2">
-        <v>46183</v>
-      </c>
-      <c r="Q9" s="9">
-        <v>0.7583333333333333</v>
-      </c>
       <c r="S9" s="1"/>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="2">
-        <v>46160</v>
-      </c>
-      <c r="E10" s="9">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L10" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P10" s="2">
-        <v>46152</v>
-      </c>
-      <c r="Q10" s="9">
-        <v>0.7583333333333333</v>
-      </c>
       <c r="S10" s="1"/>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>7</v>
       </c>
-      <c r="C11" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="2">
-        <v>46160</v>
-      </c>
-      <c r="E11" s="9">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P11" s="2">
-        <v>46166</v>
-      </c>
-      <c r="Q11" s="9">
-        <v>0.7583333333333333</v>
-      </c>
       <c r="S11" s="1"/>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B12" s="1">
         <v>8</v>
       </c>
-      <c r="C12" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D12" s="2">
-        <v>46160</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.73611111111111116</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L12" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P12" s="2">
-        <v>46213</v>
-      </c>
-      <c r="Q12" s="9">
-        <v>0.7583333333333333</v>
-      </c>
       <c r="S12" s="1"/>
     </row>
     <row r="13" spans="1:19" ht="15" x14ac:dyDescent="0.3">
       <c r="B13" s="1">
         <v>9</v>
       </c>
-      <c r="C13" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="2">
-        <v>46161</v>
-      </c>
-      <c r="E13" s="9">
-        <v>0.62916666666666665</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P13" s="2">
-        <v>46170</v>
-      </c>
-      <c r="Q13" s="9">
-        <v>0.63055555555555554</v>
-      </c>
+      <c r="C13" s="11"/>
       <c r="S13" s="1"/>
     </row>
     <row r="14" spans="1:19" ht="15" x14ac:dyDescent="0.3">
       <c r="B14" s="1">
         <v>10</v>
       </c>
-      <c r="C14" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="2">
-        <v>46161</v>
-      </c>
-      <c r="E14" s="9">
-        <v>0.6479166666666667</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="N14" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P14" s="2">
-        <v>46171</v>
-      </c>
-      <c r="Q14" s="9">
-        <v>0.64930555555555558</v>
-      </c>
+      <c r="C14" s="11"/>
       <c r="S14" s="1"/>
     </row>
     <row r="15" spans="1:19" ht="15" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="2">
-        <v>46161</v>
-      </c>
-      <c r="E15" s="9">
-        <v>0.65694444444444444</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M15" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="N15" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="O15" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P15" s="2">
-        <v>46164</v>
-      </c>
-      <c r="Q15" s="9">
-        <v>0.65694444444444444</v>
-      </c>
+      <c r="C15" s="11"/>
       <c r="S15" s="1"/>
     </row>
     <row r="16" spans="1:19" ht="15" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="D16" s="2">
-        <v>46161</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0.65694444444444444</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M16" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="N16" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P16" s="2">
-        <v>46162</v>
-      </c>
-      <c r="Q16" s="9">
-        <v>0.66180555555555554</v>
-      </c>
+      <c r="C16" s="11"/>
       <c r="S16" s="1"/>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>13</v>
       </c>
-      <c r="C17" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" s="2">
-        <v>46161</v>
-      </c>
-      <c r="E17" s="9">
-        <v>0.67013888888888884</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M17" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="N17" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P17" s="2">
-        <v>46162</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>0.87847222222222221</v>
-      </c>
       <c r="S17" s="1"/>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>14</v>
       </c>
-      <c r="C18" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="2">
-        <v>46161</v>
-      </c>
-      <c r="E18" s="9">
-        <v>0.7006944444444444</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="N18" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="O18" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P18" s="2">
-        <v>46164</v>
-      </c>
-      <c r="Q18" s="9">
-        <v>0.70138888888888884</v>
-      </c>
       <c r="S18" s="1"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.3">
       <c r="B19" s="1">
         <v>15</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" s="2">
-        <v>46163</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0.73402777777777783</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L19" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="M19" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="N19" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="P19" s="2">
-        <v>46167</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>0.73472222222222217</v>
-      </c>
       <c r="S19" s="1"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.3">
@@ -1746,6 +1113,22 @@
       <c r="B21" s="1">
         <v>17</v>
       </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="13"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="12"/>
       <c r="S21" s="1"/>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.3">
@@ -1916,15 +1299,27 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="18">
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="E1:G2"/>
     <mergeCell ref="J1:K2"/>
     <mergeCell ref="H1:I2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="F3:F4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="I3:I4"/>
+    <mergeCell ref="J3:J4"/>
+    <mergeCell ref="K3:K4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:Q100">
+  <conditionalFormatting sqref="B5:Q19 B20 B21:Q100">
     <cfRule type="expression" dxfId="9" priority="6" stopIfTrue="1">
       <formula>$P5=""</formula>
     </cfRule>
@@ -1959,6 +1354,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
@@ -1966,25 +1362,25 @@
           <x14:formula1>
             <xm:f>DADOS!$D$5:$D$23</xm:f>
           </x14:formula1>
-          <xm:sqref>J5:J23</xm:sqref>
+          <xm:sqref>J21:J23 J5:J19</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{B4A8BA25-7F51-4A4E-8C1E-CC5BB724F179}">
           <x14:formula1>
             <xm:f>DADOS!$H$5:$H$12</xm:f>
           </x14:formula1>
-          <xm:sqref>M5:M20</xm:sqref>
+          <xm:sqref>M5:M19</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" xr:uid="{0AA13D94-49AF-474D-9571-914120449489}">
           <x14:formula1>
             <xm:f>DADOS!$F$5:$F$12</xm:f>
           </x14:formula1>
-          <xm:sqref>N5:N100</xm:sqref>
+          <xm:sqref>N21:N100 N5:N19</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1C60BA97-0F1A-43D1-A48F-BAAD3868EDA8}">
           <x14:formula1>
             <xm:f>DADOS!$J$5:$J$14</xm:f>
           </x14:formula1>
-          <xm:sqref>G5:G100</xm:sqref>
+          <xm:sqref>G21:G100 G5:G19</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2006,24 +1402,24 @@
   <sheetData>
     <row r="3" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="2:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D5" t="s">
@@ -2036,11 +1432,11 @@
         <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="9" t="s">
         <v>5</v>
       </c>
       <c r="D6" t="s">
@@ -2053,11 +1449,11 @@
         <v>17</v>
       </c>
       <c r="J6" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="9" t="s">
         <v>6</v>
       </c>
       <c r="D7" t="s">
@@ -2070,11 +1466,11 @@
         <v>18</v>
       </c>
       <c r="J7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="9" t="s">
         <v>7</v>
       </c>
       <c r="D8" t="s">
@@ -2087,52 +1483,52 @@
         <v>19</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B9" s="14" t="s">
-        <v>37</v>
+      <c r="B9" s="9" t="s">
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="F9" t="s">
         <v>24</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B10" s="15"/>
+      <c r="B10" s="10"/>
       <c r="D10" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F10" t="s">
         <v>25</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B11" s="14"/>
+      <c r="B11" s="9"/>
       <c r="F11" t="s">
         <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="J12" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="J13" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/Teste_Requisições _ Topografia.xlsx
+++ b/Teste_Requisições _ Topografia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francisco\Desktop\TopogfRegisto-DEV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C14AE35A-C843-44B1-AAAC-B46A5421EA46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9762A6A1-2B89-4C8B-AEEC-18B6F2FBC943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-5445" windowWidth="38640" windowHeight="21120" xr2:uid="{27465798-F3B3-4AB2-AA5D-2EABD83C4153}"/>
   </bookViews>
@@ -351,7 +351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -385,35 +385,40 @@
     <xf numFmtId="20" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -829,7 +834,7 @@
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9.109375" style="1"/>
-    <col min="3" max="3" width="16.5546875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12.109375" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.109375" style="6" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.6640625" style="1" customWidth="1"/>
@@ -850,25 +855,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="16" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="24" t="s">
         <v>31</v>
       </c>
-      <c r="I1" s="18"/>
-      <c r="J1" s="17" t="s">
+      <c r="I1" s="24"/>
+      <c r="J1" s="23" t="s">
         <v>32</v>
       </c>
-      <c r="K1" s="17"/>
+      <c r="K1" s="23"/>
       <c r="L1" s="7"/>
       <c r="M1" s="7"/>
       <c r="N1" s="7"/>
@@ -878,89 +883,89 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:19" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="15"/>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="18"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
       <c r="S2" s="1"/>
     </row>
     <row r="3" spans="1:19" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="21"/>
-      <c r="F3" s="19" t="s">
+      <c r="E3" s="20"/>
+      <c r="F3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="J3" s="19" t="s">
+      <c r="J3" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="19" t="s">
+      <c r="K3" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="L3" s="20" t="s">
+      <c r="L3" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="M3" s="20" t="s">
+      <c r="M3" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="N3" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="24" t="s">
+      <c r="O3" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="21" t="s">
+      <c r="P3" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="Q3" s="21"/>
+      <c r="Q3" s="20"/>
       <c r="S3" s="1"/>
     </row>
     <row r="4" spans="1:19" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="19"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="22" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="20"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="24"/>
-      <c r="P4" s="22" t="s">
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="J4" s="18"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="17"/>
+      <c r="N4" s="18"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="Q4" s="23" t="s">
+      <c r="Q4" s="16" t="s">
         <v>1</v>
       </c>
       <c r="S4" s="1"/>
@@ -969,48 +974,48 @@
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D5" s="2">
         <v>46182</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="27">
         <v>0.59583333333333333</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J5" s="12" t="s">
+      <c r="J5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12" t="s">
+      <c r="L5" s="1"/>
+      <c r="M5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="N5" s="12" t="s">
+      <c r="N5" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="O5" s="12"/>
-      <c r="P5" s="13">
+      <c r="O5" s="1"/>
+      <c r="P5" s="2">
         <v>46189</v>
       </c>
-      <c r="Q5" s="14">
+      <c r="Q5" s="27">
         <v>0.59722222222222221</v>
       </c>
-      <c r="R5" s="12" t="s">
+      <c r="R5" t="s">
         <v>61</v>
       </c>
       <c r="S5" s="1"/>
@@ -1025,6 +1030,22 @@
       <c r="B7" s="1">
         <v>3</v>
       </c>
+      <c r="C7"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="26"/>
+      <c r="F7"/>
+      <c r="G7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="L7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="26"/>
+      <c r="R7"/>
       <c r="S7" s="1"/>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.3">
@@ -1300,11 +1321,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
-    <mergeCell ref="N3:N4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="D3:E3"/>
     <mergeCell ref="P3:Q3"/>
     <mergeCell ref="A1:D2"/>
     <mergeCell ref="E1:G2"/>
@@ -1318,6 +1334,11 @@
     <mergeCell ref="I3:I4"/>
     <mergeCell ref="J3:J4"/>
     <mergeCell ref="K3:K4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="D3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="B5:Q19 B20 B21:Q100">
     <cfRule type="expression" dxfId="9" priority="6" stopIfTrue="1">
